--- a/artfynd/A 30922-2026 artfynd.xlsx
+++ b/artfynd/A 30922-2026 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>135769358</v>
       </c>
       <c r="B6" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
